--- a/data/trans_orig/IP09B02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP09B02-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2007 (tasa de respuesta: 98,55%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>47,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>22018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29927</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39752</t>
+          <t>39129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50344</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>19621</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12968</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>61042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72284</t>
+          <t>72400</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>98413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114986</t>
+          <t>114016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39055</t>
+          <t>39292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2012 (tasa de respuesta: 97,74%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2012 (tasa de respuesta: 97,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16874</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19649</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30154</t>
+          <t>29851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>23753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>40994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>52751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25839</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>17050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>11018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>21028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31036</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,83%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15225</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43961</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58425</t>
+          <t>58200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70547</t>
+          <t>69358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102383</t>
+          <t>102009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123457</t>
+          <t>122446</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>37783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57070</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78144</t>
+          <t>78518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11086</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>17755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22158</t>
+          <t>21757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12006</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>13378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>45337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60958</t>
+          <t>61043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>28590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54495</t>
+          <t>53233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17500</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26294</t>
+          <t>26551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10299</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>27284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36097</t>
+          <t>36287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>12883</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>20577</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28026</t>
+          <t>28072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28381</t>
+          <t>28018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39107</t>
+          <t>39052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52578</t>
+          <t>52892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65136</t>
+          <t>65726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>45687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56624</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64030</t>
+          <t>63923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82179</t>
+          <t>82207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113774</t>
+          <t>114571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134739</t>
+          <t>135763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>35106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48804</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP09B02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP09B02-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11575</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8216</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13521</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>81,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4600</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7041</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7133</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,27%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11575</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8793</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13540</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>81,61%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12252</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2608</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5967</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4736</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2295</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7334</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>50,73%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2608</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5390</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14183</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14183</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14183</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9336</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9336</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9336</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>14183</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>14183</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26487</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21188</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29956</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>75,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14309</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21694</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14486</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21637</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>75,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>58,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26487</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>22018</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>29979</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>75,37%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39129</t>
+          <t>38352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50027</t>
+          <t>49770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8654</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13953</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6023</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2971</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10356</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3028</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10179</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>24,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>8654</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5162</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>13123</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>24,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>24665</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>24665</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>24665</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13521</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>70,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10322</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7343</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12511</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7172</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12407</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>75,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13521</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9990</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>89,91%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3377</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1188</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6356</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6527</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>24,65%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1517</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5048</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13699</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>13699</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>13699</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15748</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13025</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17127</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>73,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5832</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3618</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7258</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7245</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>74,07%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>45,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15748</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12970</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17117</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -1870,67 +1870,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>26,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>2042</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4256</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4667</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>25,93%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>54,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4799</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>7874</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>7874</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>7874</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>61277</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>72241</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>74,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>39396</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33479</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44264</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32809</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>44199</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>60,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>79,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67331</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>61042</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>72400</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>81,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98413</t>
+          <t>98818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>114513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14800</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9890</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20854</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>25,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16178</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11310</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22095</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11375</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>22765</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>14800</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>9731</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>21089</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>82131</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>82131</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>82131</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>55574</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>55574</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>55574</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>82131</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>82131</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>82131</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8775</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5029</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12710</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8783</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5125</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12673</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5429</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>43,1%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8775</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5408</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13003</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,74%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13304</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9369</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17050</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11598</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7708</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15256</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8037</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14952</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>56,9%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13304</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9076</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>16671</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>60,26%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>19612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29851</t>
+          <t>30288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22079</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22079</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22079</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>20381</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>20381</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>20381</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22079</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22079</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22079</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26303</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21164</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>30279</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>69,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>56,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>80,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>20629</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15925</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23753</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16208</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23578</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>72,92%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>56,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>83,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26303</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>21513</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30427</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>69,6%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40994</t>
+          <t>40736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52751</t>
+          <t>52602</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11490</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7514</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16629</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>7659</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12363</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12080</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>27,08%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>43,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>11490</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>7366</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16280</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>30,4%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>37793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>28288</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>28288</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>28288</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>37793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8803</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11702</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>37,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13097</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9181</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16208</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9387</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16194</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>64,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8803</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5712</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11803</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26680</t>
+          <t>26409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6158</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3259</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9327</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>62,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>7102</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3991</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11018</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10812</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6158</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3158</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9249</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18110</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>20199</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>20199</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>20199</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18126</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14425</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21165</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>77,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>61,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8766</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11352</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5354</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11267</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>65,54%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>43,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>84,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18126</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13895</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,36%</t>
         </is>
       </c>
     </row>
@@ -3817,67 +3817,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>5325</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2286</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9026</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>4609</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7499</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>34,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5325</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2423</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9556</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>23451</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>23451</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>23451</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>13375</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>13375</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>13375</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>23451</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>23451</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>23451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54369</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69759</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,32%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>51274</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>44459</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>58200</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>43562</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>57908</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>62,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>62007</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>54405</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>69358</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102009</t>
+          <t>101791</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122446</t>
+          <t>122853</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36277</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28525</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>43915</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>30968</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>37783</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>24334</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>38680</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>36277</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>28926</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>43879</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58081</t>
+          <t>57674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>78736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>98284</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>98284</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>98284</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>98284</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>98284</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>98284</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5346</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2572</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8221</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2111</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4422</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4367</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5346</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8132</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,33%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7285</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4410</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10059</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>57,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7571</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5260</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9152</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9175</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>78,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>54,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7285</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4499</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10089</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>57,67%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9682</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9682</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9682</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14785</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>53,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11731</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8398</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14566</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8335</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14467</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>63,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11255</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7346</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15131</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>53,42%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27598</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,68%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9814</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6284</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13890</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6785</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10118</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10181</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>36,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>54,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9814</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>13723</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>46,58%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21757</t>
+          <t>21735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>18516</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>18516</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>18516</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3615</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5194</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5627</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7773</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2870</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>67,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3615</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5204</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>60,95%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2316</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4495</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2752</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5248</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5509</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>32,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2316</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4557</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,05%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8379</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>8379</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>8379</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8214</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10456</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>69,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>46,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>88,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4723</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1726</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7585</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>44,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8214</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5069</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10411</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>69,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,01%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3602</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6365</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>30,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5822</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8819</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3143</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>55,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3602</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6747</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>30,49%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>10545</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>10545</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>10545</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22300</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34394</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24192</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18533</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29516</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18689</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29474</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>51,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>28429</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22748</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34242</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45337</t>
+          <t>44687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23018</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17053</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29147</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>22931</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17607</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28590</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17649</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>28434</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23018</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>17205</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>28699</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,74%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37527</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53233</t>
+          <t>53883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4722</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6998</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>27,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,43%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2444</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6856</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>57,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6815</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>72,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3499</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5729</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>42,81%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>11346</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>66,01%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13040</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9602</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15481</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>50,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>81,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7410</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4506</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8877</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>79,74%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>48,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>22795</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26551</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5863</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9301</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1882</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4786</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>51,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16456</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12611</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19300</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>76,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14303</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10299</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15944</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32326</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27284</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36287</t>
+          <t>34607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5095</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2251</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8940</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2435</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6439</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31465</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25440</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36144</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>80,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25155</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20577</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28072</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34355</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28018</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39052</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>59510</t>
+          <t>52439</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52892</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65726</t>
+          <t>57692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7551</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2872</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13576</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,8%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4191</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8769</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11328</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65683</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58089</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>73728</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>65,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>51540</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>45687</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>56596</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>71,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82207</t>
+          <t>51248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>124989</t>
+          <t>112525</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>102983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135763</t>
+          <t>121641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23188</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15143</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30782</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>12008</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6952</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17861</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35106</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48007</t>
+          <t>44970</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
